--- a/data/trans_dic/P15A-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P15A-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,57 +717,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,91</t>
+          <t>2,05; 5,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,38</t>
+          <t>1,14; 3,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,75</t>
+          <t>1,43; 3,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,17</t>
+          <t>1,43; 4,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,74</t>
+          <t>1,34; 3,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,29</t>
+          <t>2,3; 5,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,31</t>
+          <t>1,65; 4,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,91</t>
+          <t>2,07; 3,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,86</t>
+          <t>1,97; 3,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,7</t>
+          <t>1,93; 3,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,43</t>
+          <t>1,87; 3,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,93</t>
+          <t>3,13; 5,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,32</t>
+          <t>1,98; 4,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,52</t>
+          <t>2,17; 4,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,5</t>
+          <t>1,1; 3,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,46</t>
+          <t>2,11; 4,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,91</t>
+          <t>1,88; 4,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,54</t>
+          <t>1,45; 3,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,32</t>
+          <t>1,9; 4,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 4,73</t>
+          <t>2,96; 4,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,71</t>
+          <t>2,13; 3,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,59</t>
+          <t>2,03; 3,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,43</t>
+          <t>1,67; 3,52</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,34</t>
+          <t>2,27; 5,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,11</t>
+          <t>1,56; 4,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,67</t>
+          <t>0,81; 2,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,98</t>
+          <t>0,83; 2,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,18</t>
+          <t>2,33; 5,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,16</t>
+          <t>1,69; 4,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,39</t>
+          <t>0,69; 2,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,38</t>
+          <t>1,0; 3,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,66</t>
+          <t>2,63; 4,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,68</t>
+          <t>1,9; 3,66</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,3</t>
+          <t>0,98; 2,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,74</t>
+          <t>1,24; 2,74</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,97</t>
+          <t>2,49; 4,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,99</t>
+          <t>2,53; 5,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,12</t>
+          <t>1,93; 4,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,98</t>
+          <t>1,17; 2,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,44</t>
+          <t>1,4; 3,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,46</t>
+          <t>1,52; 3,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,66</t>
+          <t>2,18; 4,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,1</t>
+          <t>1,52; 3,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,7</t>
+          <t>2,2; 3,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,75</t>
+          <t>2,21; 3,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 4,07</t>
+          <t>2,39; 4,05</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,66</t>
+          <t>1,55; 2,65</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,42</t>
+          <t>3,15; 4,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,56</t>
+          <t>2,34; 3,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,19</t>
+          <t>2,09; 3,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,82</t>
+          <t>1,52; 2,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,4</t>
+          <t>2,23; 3,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,38</t>
+          <t>2,21; 3,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,11</t>
+          <t>1,95; 3,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,13</t>
+          <t>1,96; 3,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 3,77</t>
+          <t>2,87; 3,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,24</t>
+          <t>2,43; 3,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 2,97</t>
+          <t>2,2; 2,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 2,71</t>
+          <t>1,88; 2,69</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14646; 34081</t>
+          <t>14203; 34820</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8388; 23747</t>
+          <t>8007; 22060</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9591; 25324</t>
+          <t>9639; 25751</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9705; 32846</t>
+          <t>9094; 30904</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9647; 25733</t>
+          <t>9210; 24952</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14938; 36904</t>
+          <t>16023; 38351</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11469; 29021</t>
+          <t>11082; 28287</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14190; 26427</t>
+          <t>14014; 26550</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28013; 53308</t>
+          <t>27199; 50664</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26830; 51762</t>
+          <t>27062; 52036</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24090; 46167</t>
+          <t>25237; 48396</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26877; 51207</t>
+          <t>26889; 51237</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30944; 57041</t>
+          <t>30068; 57193</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20461; 43932</t>
+          <t>20206; 44767</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22507; 46221</t>
+          <t>22238; 45199</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12388; 41790</t>
+          <t>13071; 42297</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20213; 43206</t>
+          <t>20460; 42737</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19062; 40334</t>
+          <t>19453; 42113</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14595; 36918</t>
+          <t>15115; 37087</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18920; 41418</t>
+          <t>18182; 39975</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54950; 91354</t>
+          <t>57130; 91522</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44320; 76096</t>
+          <t>43611; 74677</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43431; 74249</t>
+          <t>41963; 73522</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35567; 73777</t>
+          <t>35898; 75748</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15752; 36220</t>
+          <t>15404; 35548</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11892; 31111</t>
+          <t>11837; 30755</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6413; 20301</t>
+          <t>6161; 20530</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6249; 20994</t>
+          <t>5829; 20468</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15164; 35416</t>
+          <t>15904; 35199</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13639; 32295</t>
+          <t>13128; 32330</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5332; 18773</t>
+          <t>5451; 19065</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10569; 31570</t>
+          <t>9339; 31264</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35328; 63457</t>
+          <t>35861; 62853</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28833; 56550</t>
+          <t>29206; 56108</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14649; 35457</t>
+          <t>15125; 34592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19785; 44824</t>
+          <t>20235; 44823</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24117; 46814</t>
+          <t>23433; 45739</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23418; 47260</t>
+          <t>23950; 47909</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18487; 38612</t>
+          <t>18131; 39811</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10679; 27611</t>
+          <t>10854; 27748</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15135; 35691</t>
+          <t>14560; 35443</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14808; 36401</t>
+          <t>16040; 36014</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23984; 48634</t>
+          <t>22710; 49891</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17469; 33908</t>
+          <t>16638; 33569</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>42691; 73266</t>
+          <t>43535; 73203</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>43365; 74965</t>
+          <t>44121; 75939</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>47491; 80737</t>
+          <t>47332; 80220</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31674; 53788</t>
+          <t>31342; 53542</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>102111; 144855</t>
+          <t>103130; 147090</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>80016; 122151</t>
+          <t>80175; 120595</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72684; 108185</t>
+          <t>71065; 108483</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54522; 97424</t>
+          <t>52714; 97446</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>75288; 115059</t>
+          <t>75267; 116065</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79889; 120306</t>
+          <t>78736; 119152</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>71030; 110136</t>
+          <t>69056; 107560</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>73012; 114774</t>
+          <t>71915; 111038</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>189848; 251213</t>
+          <t>190759; 249424</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>167014; 226559</t>
+          <t>169870; 228695</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>150790; 205997</t>
+          <t>152738; 206076</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>134783; 193208</t>
+          <t>133759; 191295</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15A-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P15A-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,02</t>
+          <t>2,05; 4,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,14</t>
+          <t>1,07; 3,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,82</t>
+          <t>1,42; 3,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,86</t>
+          <t>1,46; 5,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,62</t>
+          <t>1,3; 3,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,5</t>
+          <t>2,23; 5,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,2</t>
+          <t>1,7; 4,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,93</t>
+          <t>1,94; 3,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,66</t>
+          <t>2,04; 3,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 3,72</t>
+          <t>2,0; 3,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,59</t>
+          <t>1,85; 3,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,91</t>
+          <t>2,06; 3,97</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,95</t>
+          <t>3,22; 6,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,4</t>
+          <t>1,88; 4,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,42</t>
+          <t>2,28; 4,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,55</t>
+          <t>1,95; 4,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,41</t>
+          <t>2,1; 4,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,08</t>
+          <t>1,78; 3,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,56</t>
+          <t>1,38; 3,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,17</t>
+          <t>1,94; 4,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,74</t>
+          <t>2,96; 4,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,64</t>
+          <t>2,17; 3,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,56</t>
+          <t>2,07; 3,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,52</t>
+          <t>2,16; 3,81</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,24</t>
+          <t>2,24; 5,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,06</t>
+          <t>1,66; 3,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,7</t>
+          <t>0,91; 2,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,9</t>
+          <t>1,06; 3,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,15</t>
+          <t>2,32; 5,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,16</t>
+          <t>1,67; 4,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,43</t>
+          <t>0,66; 2,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,35</t>
+          <t>2,02; 3,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,61</t>
+          <t>2,59; 4,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,66</t>
+          <t>1,92; 3,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,24</t>
+          <t>0,99; 2,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,74</t>
+          <t>1,69; 3,08</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,85</t>
+          <t>2,48; 5,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,06</t>
+          <t>2,5; 4,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,25</t>
+          <t>1,95; 4,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,99</t>
+          <t>1,05; 2,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,41</t>
+          <t>1,44; 3,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,42</t>
+          <t>1,52; 3,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,78</t>
+          <t>2,3; 4,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,07</t>
+          <t>1,65; 3,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,7</t>
+          <t>2,21; 3,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,8</t>
+          <t>2,23; 3,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,05</t>
+          <t>2,4; 4,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,65</t>
+          <t>1,55; 2,67</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,27 +1244,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>2,5%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,49</t>
+          <t>3,14; 4,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,52</t>
+          <t>2,3; 3,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,2</t>
+          <t>2,09; 3,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,82</t>
+          <t>1,84; 3,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,43</t>
+          <t>2,25; 3,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,35</t>
+          <t>2,26; 3,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,03</t>
+          <t>1,97; 3,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,03</t>
+          <t>2,22; 3,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,87; 3,75</t>
+          <t>2,86; 3,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,27</t>
+          <t>2,41; 3,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 2,97</t>
+          <t>2,2; 2,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 2,69</t>
+          <t>2,15; 2,92</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16586</t>
+          <t>18863</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19143</t>
+          <t>20358</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35729</t>
+          <t>39221</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14203; 34820</t>
+          <t>14230; 33460</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8007; 22060</t>
+          <t>7535; 22463</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9639; 25751</t>
+          <t>9604; 24860</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9094; 30904</t>
+          <t>10101; 34845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9210; 24952</t>
+          <t>8944; 24731</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16023; 38351</t>
+          <t>15552; 36300</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11082; 28287</t>
+          <t>11454; 29703</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14014; 26550</t>
+          <t>14230; 27756</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27199; 50664</t>
+          <t>28188; 51478</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27062; 52036</t>
+          <t>28071; 52434</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25237; 48396</t>
+          <t>24889; 47640</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26889; 51237</t>
+          <t>29270; 56469</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26822</t>
+          <t>30790</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27542</t>
+          <t>30368</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>54364</t>
+          <t>61158</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30068; 57193</t>
+          <t>30991; 57770</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20206; 44767</t>
+          <t>19117; 42627</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22238; 45199</t>
+          <t>23292; 47555</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13071; 42297</t>
+          <t>20488; 46683</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20460; 42737</t>
+          <t>20376; 42237</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19453; 42113</t>
+          <t>18411; 39704</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15115; 37087</t>
+          <t>14399; 36382</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18182; 39975</t>
+          <t>20790; 45271</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57130; 91522</t>
+          <t>57169; 91152</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43611; 74677</t>
+          <t>44453; 76397</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41963; 73522</t>
+          <t>42659; 74838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35898; 75748</t>
+          <t>45816; 80750</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12016</t>
+          <t>15161</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20650</t>
+          <t>22430</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32665</t>
+          <t>37591</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15404; 35548</t>
+          <t>15170; 35820</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11837; 30755</t>
+          <t>12546; 30266</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6161; 20530</t>
+          <t>6933; 20862</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5829; 20468</t>
+          <t>8544; 26787</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15904; 35199</t>
+          <t>15860; 35415</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13128; 32330</t>
+          <t>13009; 31959</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5451; 19065</t>
+          <t>5184; 18906</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9339; 31264</t>
+          <t>16399; 32016</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35861; 62853</t>
+          <t>35334; 63876</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29206; 56108</t>
+          <t>29449; 56973</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15125; 34592</t>
+          <t>15298; 34168</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20235; 44823</t>
+          <t>27319; 49683</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17506</t>
+          <t>17528</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>24151</t>
+          <t>26283</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41657</t>
+          <t>43811</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23433; 45739</t>
+          <t>23333; 47233</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23950; 47909</t>
+          <t>23723; 47175</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18131; 39811</t>
+          <t>18327; 39420</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10854; 27748</t>
+          <t>10416; 26868</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14560; 35443</t>
+          <t>14979; 34794</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16040; 36014</t>
+          <t>15979; 35828</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22710; 49891</t>
+          <t>24025; 48443</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16638; 33569</t>
+          <t>18504; 35431</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43535; 73203</t>
+          <t>43780; 76801</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44121; 75939</t>
+          <t>44547; 74505</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>47332; 80220</t>
+          <t>47560; 79324</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31342; 53542</t>
+          <t>32732; 56345</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72930</t>
+          <t>82343</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>91486</t>
+          <t>99438</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>164416</t>
+          <t>181781</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>103130; 147090</t>
+          <t>102848; 146963</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>80175; 120595</t>
+          <t>78985; 119930</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71065; 108483</t>
+          <t>70895; 108804</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52714; 97446</t>
+          <t>65126; 107011</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>75267; 116065</t>
+          <t>75895; 113942</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78736; 119152</t>
+          <t>80274; 120256</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>69056; 107560</t>
+          <t>69712; 110150</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>71915; 111038</t>
+          <t>82827; 119612</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>190759; 249424</t>
+          <t>190398; 247827</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>169870; 228695</t>
+          <t>168303; 227313</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>152738; 206076</t>
+          <t>152632; 205724</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>133759; 191295</t>
+          <t>156515; 211970</t>
         </is>
       </c>
     </row>
